--- a/04_DESIGN_TABLES/DesignTable_1501_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_1501_SW2.xlsx
@@ -877,13 +877,13 @@
         <v>0.44</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -1085,13 +1085,13 @@
         <v>0.22</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
@@ -1288,13 +1288,13 @@
         <v>0.25</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.14434</v>
+        <v>0.14384</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.14434</v>
+        <v>0.14384</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.28868</v>
+        <v>0.28818</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
@@ -1496,13 +1496,13 @@
         <v>0.25</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.14434</v>
+        <v>0.14384</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.14434</v>
+        <v>0.14384</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.28868</v>
+        <v>0.28818</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
@@ -1704,13 +1704,13 @@
         <v>0.375</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
@@ -1912,13 +1912,13 @@
         <v>0.375</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
@@ -2115,13 +2115,13 @@
         <v>0.375</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
@@ -2323,13 +2323,13 @@
         <v>0.435</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.25115</v>
+        <v>0.25065</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.25115</v>
+        <v>0.25065</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.50229</v>
+        <v>0.50179</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
@@ -2531,13 +2531,13 @@
         <v>0.44</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
@@ -2739,13 +2739,13 @@
         <v>0.53</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.306</v>
+        <v>0.3055</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.306</v>
+        <v>0.3055</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.61199</v>
+        <v>0.61149</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
@@ -2942,13 +2942,13 @@
         <v>0.53</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.306</v>
+        <v>0.3055</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.306</v>
+        <v>0.3055</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.61199</v>
+        <v>0.61149</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
@@ -3150,13 +3150,13 @@
         <v>0.655</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.37816</v>
+        <v>0.37766</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.37816</v>
+        <v>0.37766</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.7563299999999999</v>
+        <v>0.75583</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
@@ -3353,13 +3353,13 @@
         <v>0.655</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.37816</v>
+        <v>0.37766</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.37816</v>
+        <v>0.37766</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.7563299999999999</v>
+        <v>0.75583</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
@@ -3561,13 +3561,13 @@
         <v>0.655</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.37816</v>
+        <v>0.37766</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.37816</v>
+        <v>0.37766</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.7563299999999999</v>
+        <v>0.75583</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
@@ -3769,13 +3769,13 @@
         <v>0.655</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.37816</v>
+        <v>0.37766</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.37816</v>
+        <v>0.37766</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.7563299999999999</v>
+        <v>0.75583</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
@@ -3977,13 +3977,13 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.94108</v>
+        <v>0.94058</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
@@ -4185,13 +4185,13 @@
         <v>1.25</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.72119</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.72119</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.44338</v>
+        <v>1.44288</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>

--- a/04_DESIGN_TABLES/DesignTable_1501_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_1501_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ18"/>
+  <dimension ref="A1:BJ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3826,35 +3826,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1501-20-20-FG</t>
+          <t>1501-16-20-FG</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8125</v>
       </c>
       <c r="D17" t="n">
-        <v>0.81335</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7068</v>
+        <v>0.6828</v>
       </c>
       <c r="F17" t="n">
         <v>1.7899</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2632</v>
+        <v>0.2572</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8125</v>
       </c>
       <c r="J17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="K17" t="n">
         <v>0.695</v>
@@ -3875,7 +3875,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.08542</v>
+        <v>1.08253</v>
       </c>
       <c r="R17" t="n">
         <v>0.819</v>
@@ -3902,43 +3902,43 @@
         <v>0.6405</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.88</v>
+        <v>1.875</v>
       </c>
       <c r="AB17" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.25</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AE17" t="n">
         <v>1.01</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.6267</v>
+        <v>1.2832</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.7068</v>
+        <v>0.6828</v>
       </c>
       <c r="AI17" t="n">
         <v>0.08696</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.81335</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.74378</v>
+        <v>0.57203</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AM17" t="n">
         <v>1.555</v>
@@ -3956,43 +3956,43 @@
         <v>0.84707</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.63</v>
+        <v>1.625</v>
       </c>
       <c r="AT17" t="n">
         <v>1.41</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.63</v>
+        <v>1.625</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8125</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8125</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.47004</v>
+        <v>0.4686</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.47004</v>
+        <v>0.4686</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.94058</v>
+        <v>0.93769</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>1501-20-20-FG</t>
+          <t>1501-16-20-FG</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 1 1/4-11 1/2 NPTF x 1 1/4-11 1/2 NPSM (female swivel)</t>
+          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 1-11 1/2 NPTF x 1 1/4-11 1/2 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF</t>
+          <t>1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -4017,223 +4017,639 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>Air-Way s113 only (double-pass 48 rows) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging); NUT FACE AT AIR-WAY W3 AND STEM TIP AT AIR-WAY M1/M (crossing to the stem tip) (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1501-16-20 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N1@DRIVE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-16-20-FG col "L LGTH" = "2.350" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.3, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the male NPTF tip (column mapping: REPORT.md, table 1501); M1@DRIVE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-16-20-FG col "M LGTH" = "1.730" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.3, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the NPSM swivel stem tip (column mapping: REPORT.md, table 1501); W3@HEX: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-16-20-FG col "M1 LGTH" = "2.150" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.3, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the swivel-nut face (column mapping: REPORT.md, table 1501); CHEX@HEX: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-16-20-FG col "C HEX" = "1.875" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.3, page verified True) [Brennan = yes 2026-10-18] - swivel nut hex (column mapping: REPORT.md, table 1501); C1HEX@HEX: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-16-20-FG col "Y FLATS" = "1.625" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.3, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 1501); D2@BORE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-16-20-FG col "A1 DRILL" = "0.938" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.3, page verified True) [Brennan = yes 2026-10-18] - male NPTF end drill (column mapping: REPORT.md, table 1501); D@BORE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-16-20-FG col "A2 DRILL" = "1.010" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.3, page verified True) [Brennan = yes 2026-10-18] - NPSM swivel stem bore (column mapping: REPORT.md, table 1501); THDMAJ_A@DRIVE: end library: pipe OD of the -16 NPTF thread = 1.315 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[16], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A1@DRIVE: end library: pipe OD of the -20 NPSM swivel thread = 1.66 (ASME B1.20.1 pipe OD, ms51500.py NPTF[20]; the value every built 1501 / 1405 / 1502 row carries for its NPSM end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes in the format of the table's other rows; = Brennan TFA-p020-t01 thread columns (A1 NPTF 1-11-1/2, A2 NPSM 1-1/4-11-1/2) and OMi Items Side 1 / 2 / 3 Thread | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging); NUT FACE AT AIR-WAY W3 AND STEM TIP AT AIR-WAY M1/M (crossing to the stem tip) (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>leg 1: male NPTF thread dia at L2 1.6709 vs hex flats 1.6300 (round end proud of the flats by 0.0204; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1501-16-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>1501-20-20-FG</t>
+          <t>1501-16-20-FG</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1501-32-32-FG</t>
+          <t>1501-20-16-FG</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.13</v>
+        <v>2.38</v>
       </c>
       <c r="C18" t="n">
-        <v>1.25</v>
+        <v>0.8125</v>
       </c>
       <c r="D18" t="n">
-        <v>1.16929</v>
+        <v>0.81335</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7565</v>
+        <v>0.7068</v>
       </c>
       <c r="F18" t="n">
         <v>1.7899</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2735</v>
+        <v>0.2632</v>
       </c>
       <c r="H18" t="n">
-        <v>2.62</v>
+        <v>2.05</v>
       </c>
       <c r="I18" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.7098</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.86603</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.6465</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.6055</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.6465</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.7447</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.4845</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1.25</v>
       </c>
-      <c r="J18" t="n">
-        <v>1.155</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1.0215</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.2766</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0.5629999999999999</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.51843</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.1755</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.134</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.502</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.1755</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.2125</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0.9385</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.0985</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0.5629999999999999</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AD18" t="n">
-        <v>3.13</v>
+        <v>2.38</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.72</v>
+        <v>0.83</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.62</v>
+        <v>2.05</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.33859</v>
+        <v>1.6267</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.7565</v>
+        <v>0.7068</v>
       </c>
       <c r="AI18" t="n">
         <v>0.08696</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.16929</v>
+        <v>0.81335</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.09973</v>
+        <v>0.74378</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.13</v>
+        <v>2.38</v>
       </c>
       <c r="AM18" t="n">
-        <v>2.268</v>
+        <v>1.211</v>
       </c>
       <c r="AN18" t="n">
-        <v>0.5435</v>
+        <v>0.469</v>
       </c>
       <c r="AO18" t="n">
         <v>0.08696</v>
       </c>
       <c r="AP18" t="n">
+        <v>0.6055</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0.6750699999999999</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0.93769</v>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>1501-20-16-FG</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 1 1/4-11 1/2 NPTF x 1-11 1/2 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>1501</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>1-11 1/2 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1501-20-16 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N1@DRIVE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-20-16-FG col "L LGTH" = "2.380" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 435.5, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the male NPTF tip (column mapping: REPORT.md, table 1501); M1@DRIVE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-20-16-FG col "M LGTH" = "1.700" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 435.5, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the NPSM swivel stem tip (column mapping: REPORT.md, table 1501); W3@HEX: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-20-16-FG col "M1 LGTH" = "2.050" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 435.5, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the swivel-nut face (column mapping: REPORT.md, table 1501); CHEX@HEX: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-20-16-FG col "C HEX" = "1.500" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 435.5, page verified True) [Brennan = yes 2026-10-18] - swivel nut hex (column mapping: REPORT.md, table 1501); C1HEX@HEX: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-20-16-FG col "Y FLATS" = "1.625" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 435.5, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 1501); D2@BORE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-20-16-FG col "A1 DRILL" = "1.250" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 435.5, page verified True) [Brennan = yes 2026-10-18] - male NPTF end drill (column mapping: REPORT.md, table 1501); D@BORE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-20-16-FG col "A2 DRILL" = "0.830" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 435.5, page verified True) [Brennan = yes 2026-10-18] - NPSM swivel stem bore (column mapping: REPORT.md, table 1501); THDMAJ_A@DRIVE: end library: pipe OD of the -20 NPTF thread = 1.66 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[20], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A1@DRIVE: end library: pipe OD of the -16 NPSM swivel thread = 1.315 (ASME B1.20.1 pipe OD, ms51500.py NPTF[16]; the value every built 1501 / 1405 / 1502 row carries for its NPSM end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes in the format of the table's other rows; = Brennan TFA-p020-t01 thread columns (A1 NPTF 1-1/4-11-1/2, A2 NPSM 1-11-1/2) and OMi Items Side 1 / 2 / 3 Thread | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging); NUT FACE AT AIR-WAY W3 AND STEM TIP AT AIR-WAY M1/M (crossing to the stem tip) (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1501-20-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate) | leg 1: male NPTF thread dia at L2 1.6709 vs hex flats 1.6250 (round end proud of the flats by 0.0229; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>1501-20-16-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1501-20-20-FG</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.9048</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.08542</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.7775</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.8141</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.6405</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.6267</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.74378</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.555</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0.5385</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0.7775</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0.84707</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0.47004</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.47004</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0.94058</v>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>1501-20-20-FG</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 1 1/4-11 1/2 NPTF x 1 1/4-11 1/2 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>1501</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>Air-Way s113 only (double-pass 48 rows) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging); NUT FACE AT AIR-WAY W3 AND STEM TIP AT AIR-WAY M1/M (crossing to the stem tip) (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>leg 1: male NPTF thread dia at L2 1.6709 vs hex flats 1.6300 (round end proud of the flats by 0.0204; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>1501-20-20-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1501-32-32-FG</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.155</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.0215</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.2766</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.51843</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.1755</v>
+      </c>
+      <c r="S20" t="n">
         <v>1.134</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="T20" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.1755</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.2125</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.9385</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.0985</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.33859</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.09973</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>2.268</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0.5435</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="AQ20" t="n">
         <v>1.20357</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="AR20" t="n">
         <v>2.62</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="AS20" t="n">
         <v>2.5</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="AT20" t="n">
         <v>2.1</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="AU20" t="n">
         <v>2.5</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="AV20" t="n">
         <v>1.465</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="AW20" t="n">
         <v>1.25</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="AX20" t="n">
         <v>1.25</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="AY20" t="n">
         <v>0.72119</v>
       </c>
-      <c r="AZ18" t="n">
+      <c r="AZ20" t="n">
         <v>0.72119</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BA20" t="n">
         <v>1.44288</v>
       </c>
-      <c r="BB18" t="inlineStr">
+      <c r="BB20" t="inlineStr">
         <is>
           <t>1501-32-32-FG</t>
         </is>
       </c>
-      <c r="BC18" t="inlineStr">
+      <c r="BC20" t="inlineStr">
         <is>
           <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 2-11 1/2 NPTF x 2-11 1/2 NPSM (female swivel)</t>
         </is>
       </c>
-      <c r="BD18" t="inlineStr">
+      <c r="BD20" t="inlineStr">
         <is>
           <t>1501</t>
         </is>
       </c>
-      <c r="BE18" t="inlineStr">
+      <c r="BE20" t="inlineStr">
         <is>
           <t>2-11 1/2 NPTF</t>
         </is>
       </c>
-      <c r="BF18" t="inlineStr">
+      <c r="BF20" t="inlineStr">
         <is>
           <t>2-11 1/2 NPSM (female swivel)</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr">
+      <c r="BG20" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="BH18" t="inlineStr">
+      <c r="BH20" t="inlineStr">
         <is>
           <t>Air-Way s113 only (double-pass 48 rows) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging); NUT FACE AT AIR-WAY W3 AND STEM TIP AT AIR-WAY M1/M (crossing to the stem tip) (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="BI18" t="inlineStr">
+      <c r="BI20" t="inlineStr">
         <is>
           <t>leg 2 hex arm 1.465 barely clears the corner puck (radius 1.443)</t>
         </is>
       </c>
-      <c r="BJ18" t="inlineStr">
+      <c r="BJ20" t="inlineStr">
         <is>
           <t>1501-32-32-FG</t>
         </is>

--- a/04_DESIGN_TABLES/DesignTable_1501_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_1501_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ20"/>
+  <dimension ref="A1:BJ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1345,7 +1345,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1501-04-04-FG</t>
+          <t>1501-04-02-FG</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1367,67 +1367,67 @@
         <v>0.1582</v>
       </c>
       <c r="H5" t="n">
-        <v>0.98</v>
+        <v>0.91</v>
       </c>
       <c r="I5" t="n">
         <v>0.25</v>
       </c>
       <c r="J5" t="n">
-        <v>0.58</v>
+        <v>0.43</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1825</v>
+        <v>0.129</v>
       </c>
       <c r="L5" t="n">
-        <v>0.54</v>
+        <v>0.38</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3146</v>
+        <v>0.2496</v>
       </c>
       <c r="N5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.345</v>
+        <v>0.28</v>
       </c>
       <c r="P5" t="n">
-        <v>0.28</v>
+        <v>0.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.39837</v>
+        <v>0.32332</v>
       </c>
       <c r="R5" t="n">
-        <v>0.263</v>
+        <v>0.1984</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2405</v>
+        <v>0.182</v>
       </c>
       <c r="T5" t="n">
-        <v>0.265</v>
+        <v>0.1572</v>
       </c>
       <c r="U5" t="n">
-        <v>0.263</v>
+        <v>0.1984</v>
       </c>
       <c r="V5" t="n">
-        <v>0.29</v>
+        <v>0.2275</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4459</v>
+        <v>0.3066</v>
       </c>
       <c r="X5" t="n">
-        <v>0.225</v>
+        <v>0.1725</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1485</v>
+        <v>0.117</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.28</v>
+        <v>0.2</v>
       </c>
       <c r="AC5" t="n">
         <v>0.28</v>
@@ -1436,10 +1436,10 @@
         <v>1.09</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.22</v>
+        <v>0.13</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.98</v>
+        <v>0.91</v>
       </c>
       <c r="AG5" t="n">
         <v>0.52183</v>
@@ -1460,22 +1460,22 @@
         <v>1.09</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.481</v>
+        <v>0.364</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.2875</v>
+        <v>0.1736</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.05556</v>
+        <v>0.03704</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.2405</v>
+        <v>0.182</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.28494</v>
+        <v>0.21163</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.98</v>
+        <v>0.91</v>
       </c>
       <c r="AS5" t="n">
         <v>0.5</v>
@@ -1487,7 +1487,7 @@
         <v>0.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="AW5" t="n">
         <v>0.25</v>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>1501-04-04-FG</t>
+          <t>1501-04-02-FG</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 1/4-18 NPTF x 1/4-18 NPSM (female swivel)</t>
+          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 1/4-18 NPTF x 1/8-27 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1/4-18 NPSM (female swivel)</t>
+          <t>1/8-27 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -1536,31 +1536,31 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>Air-Way s113 only (double-pass 48 rows) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging); NUT FACE AT AIR-WAY W3 AND STEM TIP AT AIR-WAY M1/M (crossing to the stem tip) (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>[BRENNAN-CELL 2026-10-20: D@BORE] Air-Way s113 only (double-pass 48 rows); D@BORE: Brennan TFA catalog p.20 table TFA-p020-t01 "MP-FPS 90 DEG ELBOW" row 1501-04-02-FG col "A2 DRILL" = 0.13 (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_index.json, page verified True) [user 2026-10-20 Q1: Air-Way value cannot be built -&gt; Brennan ("use brennans")] (Air-Way printed 0.23: the NPSM stem bore 0.23 is wider than the -02 stem tip (dia 0.234: neck wall 0.014); generator BLOCKED. Air-Way's own non-FG 1501-04-02 row prints 0.13 (this row's $COMMENT: "D printed 0.23 (sibling non-FG row 0.13)")) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging); NUT FACE AT AIR-WAY W3 AND STEM TIP AT AIR-WAY M1/M (crossing to the stem tip) (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>leg 1: male NPTF thread dia at L2 0.5469 vs hex flats 0.5000 (round end proud of the flats by 0.0235; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>D printed 0.23 (sibling non-FG row 0.13); copied as printed | 2026-10-20 D@BORE = Brennan 0.13 (Air-Way 0.23 cannot be built: the NPSM stem bore 0.23 is wider than the -02 stem tip (dia 0.234: neck wall 0.014); generator BLOCKED. Air-Way's own non-FG 1501-04-02 row prints 0.13 (this row's $COMMENT: "D printed 0.23 (sibling non-FG row 0.13)")) | leg 1: male NPTF thread dia at L2 0.5469 vs hex flats 0.5000 (round end proud of the flats by 0.0235; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>1501-04-04-FG</t>
+          <t>1501-04-02-FG</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1501-04-06-FG</t>
+          <t>1501-04-04-FG</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1.09</v>
       </c>
       <c r="C6" t="n">
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
       <c r="D6" t="n">
         <v>0.26092</v>
@@ -1575,67 +1575,67 @@
         <v>0.1582</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2</v>
+        <v>0.98</v>
       </c>
       <c r="I6" t="n">
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
       <c r="J6" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2465</v>
+        <v>0.1825</v>
       </c>
       <c r="L6" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4056</v>
+        <v>0.3146</v>
       </c>
       <c r="N6" t="n">
-        <v>0.125</v>
+        <v>0.11</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4375</v>
+        <v>0.345</v>
       </c>
       <c r="P6" t="n">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.50807</v>
+        <v>0.39837</v>
       </c>
       <c r="R6" t="n">
-        <v>0.331</v>
+        <v>0.263</v>
       </c>
       <c r="S6" t="n">
-        <v>0.306</v>
+        <v>0.2405</v>
       </c>
       <c r="T6" t="n">
         <v>0.265</v>
       </c>
       <c r="U6" t="n">
-        <v>0.331</v>
+        <v>0.263</v>
       </c>
       <c r="V6" t="n">
-        <v>0.36</v>
+        <v>0.29</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4707</v>
+        <v>0.4459</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2935</v>
+        <v>0.225</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.211</v>
+        <v>0.1485</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.88</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="AC6" t="n">
         <v>0.28</v>
@@ -1644,10 +1644,10 @@
         <v>1.09</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.2</v>
+        <v>0.98</v>
       </c>
       <c r="AG6" t="n">
         <v>0.52183</v>
@@ -1668,58 +1668,58 @@
         <v>1.09</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.612</v>
+        <v>0.481</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.29</v>
+        <v>0.2875</v>
       </c>
       <c r="AO6" t="n">
         <v>0.05556</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.306</v>
+        <v>0.2405</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.35044</v>
+        <v>0.28494</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.2</v>
+        <v>0.98</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AT6" t="n">
         <v>0.53</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.54</v>
+        <v>0.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.21601</v>
+        <v>0.14384</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.21601</v>
+        <v>0.14384</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.43251</v>
+        <v>0.28818</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>1501-04-06-FG</t>
+          <t>1501-04-04-FG</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 1/4-18 NPTF x 3/8-18 NPSM (female swivel)</t>
+          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 1/4-18 NPTF x 1/4-18 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3/8-18 NPSM (female swivel)</t>
+          <t>1/4-18 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -1749,161 +1749,161 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>leg 2: Air-Way nut face to stem tip (W - M) 0.250 vs Brennan 0.220: nut placed at Air-Way W (user decision 2026-09-24, as 1404/1405)</t>
+          <t>leg 1: male NPTF thread dia at L2 0.5469 vs hex flats 0.5000 (round end proud of the flats by 0.0235; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>1501-04-06-FG</t>
+          <t>1501-04-04-FG</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1501-06-04-FG</t>
+          <t>1501-04-06-FG</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="C7" t="n">
         <v>0.375</v>
       </c>
       <c r="D7" t="n">
-        <v>0.32823</v>
+        <v>0.26092</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4078</v>
+        <v>0.4018</v>
       </c>
       <c r="F7" t="n">
         <v>1.7899</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1522</v>
+        <v>0.1582</v>
       </c>
       <c r="H7" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="I7" t="n">
         <v>0.375</v>
       </c>
       <c r="J7" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.2465</v>
+      </c>
+      <c r="L7" t="n">
         <v>0.58</v>
       </c>
-      <c r="K7" t="n">
-        <v>0.1825</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.54</v>
-      </c>
       <c r="M7" t="n">
-        <v>0.3146</v>
+        <v>0.4056</v>
       </c>
       <c r="N7" t="n">
-        <v>0.11</v>
+        <v>0.125</v>
       </c>
       <c r="O7" t="n">
-        <v>0.345</v>
+        <v>0.4375</v>
       </c>
       <c r="P7" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.39837</v>
+        <v>0.50807</v>
       </c>
       <c r="R7" t="n">
-        <v>0.263</v>
+        <v>0.331</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2405</v>
+        <v>0.306</v>
       </c>
       <c r="T7" t="n">
         <v>0.265</v>
       </c>
       <c r="U7" t="n">
-        <v>0.263</v>
+        <v>0.331</v>
       </c>
       <c r="V7" t="n">
-        <v>0.29</v>
+        <v>0.36</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4459</v>
+        <v>0.4707</v>
       </c>
       <c r="X7" t="n">
-        <v>0.225</v>
+        <v>0.2935</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1485</v>
+        <v>0.211</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AB7" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AC7" t="n">
         <v>0.28</v>
       </c>
-      <c r="AC7" t="n">
-        <v>0.41</v>
-      </c>
       <c r="AD7" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.22</v>
+        <v>0.33</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.65645</v>
+        <v>0.52183</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.4078</v>
+        <v>0.4018</v>
       </c>
       <c r="AI7" t="n">
         <v>0.05556</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.32823</v>
+        <v>0.26092</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.28378</v>
+        <v>0.21647</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.481</v>
+        <v>0.612</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.2875</v>
+        <v>0.29</v>
       </c>
       <c r="AO7" t="n">
         <v>0.05556</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.2405</v>
+        <v>0.306</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.28494</v>
+        <v>0.35044</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AS7" t="n">
         <v>0.75</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.66</v>
+        <v>0.53</v>
       </c>
       <c r="AU7" t="n">
         <v>0.75</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.49</v>
+        <v>0.54</v>
       </c>
       <c r="AW7" t="n">
         <v>0.375</v>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>1501-06-04-FG</t>
+          <t>1501-04-06-FG</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 3/8-18 NPTF x 1/4-18 NPSM (female swivel)</t>
+          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 1/4-18 NPTF x 3/8-18 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF</t>
+          <t>1/4-18 NPTF</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1/4-18 NPSM (female swivel)</t>
+          <t>3/8-18 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -1955,16 +1955,21 @@
           <t>Air-Way s113 only (double-pass 48 rows) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging); NUT FACE AT AIR-WAY W3 AND STEM TIP AT AIR-WAY M1/M (crossing to the stem tip) (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>leg 2: Air-Way nut face to stem tip (W - M) 0.250 vs Brennan 0.220: nut placed at Air-Way W (user decision 2026-09-24, as 1404/1405)</t>
+        </is>
+      </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>1501-06-04-FG</t>
+          <t>1501-04-06-FG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1501-06-06-FG</t>
+          <t>1501-06-04-FG</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1986,67 +1991,67 @@
         <v>0.1522</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="I8" t="n">
         <v>0.375</v>
       </c>
       <c r="J8" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2465</v>
+        <v>0.1825</v>
       </c>
       <c r="L8" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4056</v>
+        <v>0.3146</v>
       </c>
       <c r="N8" t="n">
-        <v>0.125</v>
+        <v>0.11</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4375</v>
+        <v>0.345</v>
       </c>
       <c r="P8" t="n">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.50807</v>
+        <v>0.39837</v>
       </c>
       <c r="R8" t="n">
-        <v>0.331</v>
+        <v>0.263</v>
       </c>
       <c r="S8" t="n">
-        <v>0.306</v>
+        <v>0.2405</v>
       </c>
       <c r="T8" t="n">
         <v>0.265</v>
       </c>
       <c r="U8" t="n">
-        <v>0.331</v>
+        <v>0.263</v>
       </c>
       <c r="V8" t="n">
-        <v>0.36</v>
+        <v>0.29</v>
       </c>
       <c r="W8" t="n">
-        <v>0.4707</v>
+        <v>0.4459</v>
       </c>
       <c r="X8" t="n">
-        <v>0.2935</v>
+        <v>0.225</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.211</v>
+        <v>0.1485</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.88</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="AC8" t="n">
         <v>0.41</v>
@@ -2055,10 +2060,10 @@
         <v>1.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AG8" t="n">
         <v>0.65645</v>
@@ -2079,22 +2084,22 @@
         <v>1.22</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.612</v>
+        <v>0.481</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.29</v>
+        <v>0.2875</v>
       </c>
       <c r="AO8" t="n">
         <v>0.05556</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.306</v>
+        <v>0.2405</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.35044</v>
+        <v>0.28494</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AS8" t="n">
         <v>0.75</v>
@@ -2106,7 +2111,7 @@
         <v>0.75</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.54</v>
+        <v>0.49</v>
       </c>
       <c r="AW8" t="n">
         <v>0.375</v>
@@ -2125,12 +2130,12 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>1501-06-06-FG</t>
+          <t>1501-06-04-FG</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 3/8-18 NPTF x 3/8-18 NPSM (female swivel)</t>
+          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 3/8-18 NPTF x 1/4-18 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
@@ -2145,7 +2150,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3/8-18 NPSM (female swivel)</t>
+          <t>1/4-18 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -2158,28 +2163,23 @@
           <t>Air-Way s113 only (double-pass 48 rows) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging); NUT FACE AT AIR-WAY W3 AND STEM TIP AT AIR-WAY M1/M (crossing to the stem tip) (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>leg 2: Air-Way nut face to stem tip (W - M) 0.250 vs Brennan 0.220: nut placed at Air-Way W (user decision 2026-09-24, as 1404/1405)</t>
-        </is>
-      </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>1501-06-06-FG</t>
+          <t>1501-06-04-FG</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1501-06-08-FG</t>
+          <t>1501-06-06-FG</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1.22</v>
       </c>
       <c r="C9" t="n">
-        <v>0.435</v>
+        <v>0.375</v>
       </c>
       <c r="D9" t="n">
         <v>0.32823</v>
@@ -2194,67 +2194,67 @@
         <v>0.1522</v>
       </c>
       <c r="H9" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.435</v>
+        <v>0.375</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="K9" t="n">
-        <v>0.304</v>
+        <v>0.2465</v>
       </c>
       <c r="L9" t="n">
-        <v>0.72</v>
+        <v>0.58</v>
       </c>
       <c r="M9" t="n">
-        <v>0.455</v>
+        <v>0.4056</v>
       </c>
       <c r="N9" t="n">
-        <v>0.14</v>
+        <v>0.125</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.57735</v>
+        <v>0.50807</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4115</v>
+        <v>0.331</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3795</v>
+        <v>0.306</v>
       </c>
       <c r="T9" t="n">
-        <v>0.356</v>
+        <v>0.265</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4115</v>
+        <v>0.331</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4425</v>
+        <v>0.36</v>
       </c>
       <c r="W9" t="n">
-        <v>0.595</v>
+        <v>0.4707</v>
       </c>
       <c r="X9" t="n">
-        <v>0.37</v>
+        <v>0.2935</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.281</v>
+        <v>0.211</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="AC9" t="n">
         <v>0.41</v>
@@ -2263,10 +2263,10 @@
         <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.45</v>
+        <v>0.33</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AG9" t="n">
         <v>0.65645</v>
@@ -2287,58 +2287,58 @@
         <v>1.22</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.759</v>
+        <v>0.612</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.388</v>
+        <v>0.29</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.3795</v>
+        <v>0.306</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.43664</v>
+        <v>0.35044</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.87</v>
+        <v>0.75</v>
       </c>
       <c r="AT9" t="n">
         <v>0.66</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.87</v>
+        <v>0.75</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.435</v>
+        <v>0.375</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.435</v>
+        <v>0.375</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.25065</v>
+        <v>0.21601</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.25065</v>
+        <v>0.21601</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.50179</v>
+        <v>0.43251</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1501-06-08-FG</t>
+          <t>1501-06-06-FG</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 3/8-18 NPTF x 1/2-14 NPSM (female swivel)</t>
+          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 3/8-18 NPTF x 3/8-18 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1/2-14 NPSM (female swivel)</t>
+          <t>3/8-18 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -2368,185 +2368,185 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>leg 2 hex arm 0.520 barely clears the corner puck (radius 0.502); leg 2: Air-Way nut face to stem tip (W - M) 0.330 vs Brennan 0.280: nut placed at Air-Way W (user decision 2026-09-24, as 1404/1405)</t>
+          <t>leg 2: Air-Way nut face to stem tip (W - M) 0.250 vs Brennan 0.220: nut placed at Air-Way W (user decision 2026-09-24, as 1404/1405)</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>1501-06-08-FG</t>
+          <t>1501-06-06-FG</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1501-08-06-FG</t>
+          <t>1501-06-08-FG</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="C10" t="n">
-        <v>0.44</v>
+        <v>0.435</v>
       </c>
       <c r="D10" t="n">
-        <v>0.40779</v>
+        <v>0.32823</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5337</v>
+        <v>0.4078</v>
       </c>
       <c r="F10" t="n">
         <v>1.7899</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2163</v>
+        <v>0.1522</v>
       </c>
       <c r="H10" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="I10" t="n">
-        <v>0.44</v>
+        <v>0.435</v>
       </c>
       <c r="J10" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.57735</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.43664</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AT10" t="n">
         <v>0.66</v>
       </c>
-      <c r="K10" t="n">
-        <v>0.2465</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.4056</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.4375</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.50807</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.306</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.4707</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.2935</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.211</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0.81557</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0.5337</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0.07142999999999999</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0.40779</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0.35064</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0.612</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0.05556</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0.306</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0.35044</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0.72</v>
-      </c>
       <c r="AU10" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.44</v>
+        <v>0.435</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.44</v>
+        <v>0.435</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.25353</v>
+        <v>0.25065</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.25353</v>
+        <v>0.25065</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.50757</v>
+        <v>0.50179</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1501-08-06-FG</t>
+          <t>1501-06-08-FG</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 1/2-14 NPTF x 3/8-18 NPSM (female swivel)</t>
+          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 3/8-18 NPTF x 1/2-14 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF</t>
+          <t>3/8-18 NPTF</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3/8-18 NPSM (female swivel)</t>
+          <t>1/2-14 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -2576,26 +2576,26 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>leg 2: Air-Way nut face to stem tip (W - M) 0.250 vs Brennan 0.220: nut placed at Air-Way W (user decision 2026-09-24, as 1404/1405)</t>
+          <t>leg 2 hex arm 0.520 barely clears the corner puck (radius 0.502); leg 2: Air-Way nut face to stem tip (W - M) 0.330 vs Brennan 0.280: nut placed at Air-Way W (user decision 2026-09-24, as 1404/1405)</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>1501-08-06-FG</t>
+          <t>1501-06-08-FG</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1501-08-12-FG</t>
+          <t>1501-08-06-FG</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1.47</v>
       </c>
       <c r="C11" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="D11" t="n">
         <v>0.40779</v>
@@ -2610,67 +2610,67 @@
         <v>0.2163</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="I11" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="J11" t="n">
-        <v>0.78</v>
+        <v>0.66</v>
       </c>
       <c r="K11" t="n">
-        <v>0.389</v>
+        <v>0.2465</v>
       </c>
       <c r="L11" t="n">
-        <v>0.745</v>
+        <v>0.58</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5694</v>
+        <v>0.4056</v>
       </c>
       <c r="N11" t="n">
-        <v>0.135</v>
+        <v>0.125</v>
       </c>
       <c r="O11" t="n">
-        <v>0.625</v>
+        <v>0.4375</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.50807</v>
       </c>
       <c r="R11" t="n">
-        <v>0.517</v>
+        <v>0.331</v>
       </c>
       <c r="S11" t="n">
-        <v>0.485</v>
+        <v>0.306</v>
       </c>
       <c r="T11" t="n">
-        <v>0.361</v>
+        <v>0.265</v>
       </c>
       <c r="U11" t="n">
-        <v>0.517</v>
+        <v>0.331</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5625</v>
+        <v>0.36</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6189</v>
+        <v>0.4707</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4635</v>
+        <v>0.2935</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.375</v>
+        <v>0.211</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.25</v>
+        <v>0.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="AC11" t="n">
         <v>0.53</v>
@@ -2679,10 +2679,10 @@
         <v>1.47</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.63</v>
+        <v>0.33</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="AG11" t="n">
         <v>0.81557</v>
@@ -2703,58 +2703,58 @@
         <v>1.47</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.97</v>
+        <v>0.612</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.393</v>
+        <v>0.29</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.485</v>
+        <v>0.306</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.54214</v>
+        <v>0.35044</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.06</v>
+        <v>0.88</v>
       </c>
       <c r="AT11" t="n">
         <v>0.72</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.06</v>
+        <v>0.88</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.82</v>
+        <v>0.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.3055</v>
+        <v>0.25353</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.3055</v>
+        <v>0.25353</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.61149</v>
+        <v>0.50757</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>1501-08-12-FG</t>
+          <t>1501-08-06-FG</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 1/2-14 NPTF x 3/4-14 NPSM (female swivel)</t>
+          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 1/2-14 NPTF x 3/8-18 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3/4-14 NPSM (female swivel)</t>
+          <t>3/8-18 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -2782,158 +2782,163 @@
           <t>Air-Way s113 only (double-pass 48 rows) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging); NUT FACE AT AIR-WAY W3 AND STEM TIP AT AIR-WAY M1/M (crossing to the stem tip) (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>leg 2: Air-Way nut face to stem tip (W - M) 0.250 vs Brennan 0.220: nut placed at Air-Way W (user decision 2026-09-24, as 1404/1405)</t>
+        </is>
+      </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>1501-08-12-FG</t>
+          <t>1501-08-06-FG</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1501-12-08-FG</t>
+          <t>1501-08-12-FG</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="C12" t="n">
         <v>0.53</v>
       </c>
       <c r="D12" t="n">
-        <v>0.51241</v>
+        <v>0.40779</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5457</v>
+        <v>0.5337</v>
       </c>
       <c r="F12" t="n">
         <v>1.7899</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2043</v>
+        <v>0.2163</v>
       </c>
       <c r="H12" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="I12" t="n">
         <v>0.53</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="K12" t="n">
-        <v>0.304</v>
+        <v>0.389</v>
       </c>
       <c r="L12" t="n">
-        <v>0.72</v>
+        <v>0.745</v>
       </c>
       <c r="M12" t="n">
-        <v>0.455</v>
+        <v>0.5694</v>
       </c>
       <c r="N12" t="n">
-        <v>0.14</v>
+        <v>0.135</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="P12" t="n">
         <v>0.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.57735</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4115</v>
+        <v>0.517</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3795</v>
+        <v>0.485</v>
       </c>
       <c r="T12" t="n">
-        <v>0.356</v>
+        <v>0.361</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4115</v>
+        <v>0.517</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4425</v>
+        <v>0.5625</v>
       </c>
       <c r="W12" t="n">
-        <v>0.595</v>
+        <v>0.6189</v>
       </c>
       <c r="X12" t="n">
-        <v>0.37</v>
+        <v>0.4635</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.281</v>
+        <v>0.375</v>
       </c>
       <c r="Z12" t="n">
         <v>0.33</v>
       </c>
       <c r="AA12" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AB12" t="n">
         <v>0.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.72</v>
+        <v>0.53</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.42</v>
+        <v>0.63</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.02482</v>
+        <v>0.81557</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.5457</v>
+        <v>0.5337</v>
       </c>
       <c r="AI12" t="n">
         <v>0.07142999999999999</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.51241</v>
+        <v>0.40779</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.45527</v>
+        <v>0.35064</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.759</v>
+        <v>0.97</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.388</v>
+        <v>0.393</v>
       </c>
       <c r="AO12" t="n">
         <v>0.07142999999999999</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.3795</v>
+        <v>0.485</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.43664</v>
+        <v>0.54214</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="AS12" t="n">
         <v>1.06</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.84</v>
+        <v>0.72</v>
       </c>
       <c r="AU12" t="n">
         <v>1.06</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.65</v>
+        <v>0.82</v>
       </c>
       <c r="AW12" t="n">
         <v>0.53</v>
@@ -2952,12 +2957,12 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>1501-12-08-FG</t>
+          <t>1501-08-12-FG</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 3/4-14 NPTF x 1/2-14 NPSM (female swivel)</t>
+          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 1/2-14 NPTF x 3/4-14 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
@@ -2967,12 +2972,12 @@
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF</t>
+          <t>1/2-14 NPTF</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1/2-14 NPSM (female swivel)</t>
+          <t>3/4-14 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -2985,28 +2990,23 @@
           <t>Air-Way s113 only (double-pass 48 rows) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging); NUT FACE AT AIR-WAY W3 AND STEM TIP AT AIR-WAY M1/M (crossing to the stem tip) (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>leg 1: male NPTF thread dia at L2 1.0589 vs hex flats 1.0600 (round end flush with the flats by 0.0005; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012); leg 2: Air-Way nut face to stem tip (W - M) 0.330 vs Brennan 0.280: nut placed at Air-Way W (user decision 2026-09-24, as 1404/1405)</t>
-        </is>
-      </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>1501-12-08-FG</t>
+          <t>1501-08-12-FG</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1501-12-12-FG</t>
+          <t>1501-12-08-FG</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1.59</v>
       </c>
       <c r="C13" t="n">
-        <v>0.655</v>
+        <v>0.53</v>
       </c>
       <c r="D13" t="n">
         <v>0.51241</v>
@@ -3021,64 +3021,64 @@
         <v>0.2043</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="I13" t="n">
-        <v>0.655</v>
+        <v>0.53</v>
       </c>
       <c r="J13" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.389</v>
+        <v>0.304</v>
       </c>
       <c r="L13" t="n">
-        <v>0.745</v>
+        <v>0.72</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5694</v>
+        <v>0.455</v>
       </c>
       <c r="N13" t="n">
-        <v>0.135</v>
+        <v>0.14</v>
       </c>
       <c r="O13" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="P13" t="n">
         <v>0.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.57735</v>
       </c>
       <c r="R13" t="n">
-        <v>0.517</v>
+        <v>0.4115</v>
       </c>
       <c r="S13" t="n">
-        <v>0.485</v>
+        <v>0.3795</v>
       </c>
       <c r="T13" t="n">
-        <v>0.361</v>
+        <v>0.356</v>
       </c>
       <c r="U13" t="n">
-        <v>0.517</v>
+        <v>0.4115</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5625</v>
+        <v>0.4425</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6189</v>
+        <v>0.595</v>
       </c>
       <c r="X13" t="n">
-        <v>0.4635</v>
+        <v>0.37</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.375</v>
+        <v>0.281</v>
       </c>
       <c r="Z13" t="n">
         <v>0.33</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AB13" t="n">
         <v>0.4</v>
@@ -3090,10 +3090,10 @@
         <v>1.59</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.63</v>
+        <v>0.42</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="AG13" t="n">
         <v>1.02482</v>
@@ -3114,58 +3114,58 @@
         <v>1.59</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.97</v>
+        <v>0.759</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.393</v>
+        <v>0.388</v>
       </c>
       <c r="AO13" t="n">
         <v>0.07142999999999999</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.485</v>
+        <v>0.3795</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.54214</v>
+        <v>0.43664</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.31</v>
+        <v>1.06</v>
       </c>
       <c r="AT13" t="n">
         <v>0.84</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.31</v>
+        <v>1.06</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.82</v>
+        <v>0.65</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.655</v>
+        <v>0.53</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.655</v>
+        <v>0.53</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.37766</v>
+        <v>0.3055</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.37766</v>
+        <v>0.3055</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.75583</v>
+        <v>0.61149</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>1501-12-12-FG</t>
+          <t>1501-12-08-FG</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 3/4-14 NPTF x 3/4-14 NPSM (female swivel)</t>
+          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 3/4-14 NPTF x 1/2-14 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3/4-14 NPSM (female swivel)</t>
+          <t>1/2-14 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
@@ -3193,20 +3193,25 @@
           <t>Air-Way s113 only (double-pass 48 rows) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging); NUT FACE AT AIR-WAY W3 AND STEM TIP AT AIR-WAY M1/M (crossing to the stem tip) (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>leg 1: male NPTF thread dia at L2 1.0589 vs hex flats 1.0600 (round end flush with the flats by 0.0005; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012); leg 2: Air-Way nut face to stem tip (W - M) 0.330 vs Brennan 0.280: nut placed at Air-Way W (user decision 2026-09-24, as 1404/1405)</t>
+        </is>
+      </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>1501-12-12-FG</t>
+          <t>1501-12-08-FG</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1501-12-16-FG</t>
+          <t>1501-12-12-FG</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.97</v>
+        <v>1.59</v>
       </c>
       <c r="C14" t="n">
         <v>0.655</v>
@@ -3224,79 +3229,79 @@
         <v>0.2043</v>
       </c>
       <c r="H14" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="I14" t="n">
         <v>0.655</v>
       </c>
       <c r="J14" t="n">
-        <v>0.97</v>
+        <v>0.78</v>
       </c>
       <c r="K14" t="n">
-        <v>0.525</v>
+        <v>0.389</v>
       </c>
       <c r="L14" t="n">
-        <v>0.9</v>
+        <v>0.745</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7098</v>
+        <v>0.5694</v>
       </c>
       <c r="N14" t="n">
-        <v>0.175</v>
+        <v>0.135</v>
       </c>
       <c r="O14" t="n">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.86603</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6465</v>
+        <v>0.517</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6055</v>
+        <v>0.485</v>
       </c>
       <c r="T14" t="n">
-        <v>0.428</v>
+        <v>0.361</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6465</v>
+        <v>0.517</v>
       </c>
       <c r="V14" t="n">
-        <v>0.67</v>
+        <v>0.5625</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7447</v>
+        <v>0.6189</v>
       </c>
       <c r="X14" t="n">
-        <v>0.59</v>
+        <v>0.4635</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.4845</v>
+        <v>0.375</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AC14" t="n">
         <v>0.72</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.97</v>
+        <v>1.59</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.84</v>
+        <v>0.63</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AG14" t="n">
         <v>1.02482</v>
@@ -3314,37 +3319,37 @@
         <v>0.45527</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.97</v>
+        <v>1.59</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.211</v>
+        <v>0.97</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.469</v>
+        <v>0.393</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.6055</v>
+        <v>0.485</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.6750699999999999</v>
+        <v>0.54214</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AS14" t="n">
         <v>1.31</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.22</v>
+        <v>0.84</v>
       </c>
       <c r="AU14" t="n">
         <v>1.31</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="AW14" t="n">
         <v>0.655</v>
@@ -3363,12 +3368,12 @@
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>1501-12-16-FG</t>
+          <t>1501-12-12-FG</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 3/4-14 NPTF x 1-11 1/2 NPSM (female swivel)</t>
+          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 3/4-14 NPTF x 3/4-14 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
@@ -3383,7 +3388,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPSM (female swivel)</t>
+          <t>3/4-14 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
@@ -3396,21 +3401,16 @@
           <t>Air-Way s113 only (double-pass 48 rows) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging); NUT FACE AT AIR-WAY W3 AND STEM TIP AT AIR-WAY M1/M (crossing to the stem tip) (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>leg 2: Air-Way nut face to stem tip (W - M) 0.380 vs Brennan 0.350: nut placed at Air-Way W (user decision 2026-09-24, as 1404/1405)</t>
-        </is>
-      </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>1501-12-16-FG</t>
+          <t>1501-12-12-FG</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1501-16-12-FG</t>
+          <t>1501-12-16-FG</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -3420,139 +3420,139 @@
         <v>0.655</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.51241</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6828</v>
+        <v>0.5457</v>
       </c>
       <c r="F15" t="n">
         <v>1.7899</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2572</v>
+        <v>0.2043</v>
       </c>
       <c r="H15" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="I15" t="n">
         <v>0.655</v>
       </c>
       <c r="J15" t="n">
-        <v>0.79</v>
+        <v>0.97</v>
       </c>
       <c r="K15" t="n">
-        <v>0.389</v>
+        <v>0.525</v>
       </c>
       <c r="L15" t="n">
-        <v>0.745</v>
+        <v>0.9</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5694</v>
+        <v>0.7098</v>
       </c>
       <c r="N15" t="n">
-        <v>0.135</v>
+        <v>0.175</v>
       </c>
       <c r="O15" t="n">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.86603</v>
       </c>
       <c r="R15" t="n">
-        <v>0.517</v>
+        <v>0.6465</v>
       </c>
       <c r="S15" t="n">
-        <v>0.485</v>
+        <v>0.6055</v>
       </c>
       <c r="T15" t="n">
-        <v>0.361</v>
+        <v>0.428</v>
       </c>
       <c r="U15" t="n">
-        <v>0.517</v>
+        <v>0.6465</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5625</v>
+        <v>0.67</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6189</v>
+        <v>0.7447</v>
       </c>
       <c r="X15" t="n">
-        <v>0.4635</v>
+        <v>0.59</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.375</v>
+        <v>0.4845</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="AD15" t="n">
         <v>1.97</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.63</v>
+        <v>0.84</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.2832</v>
+        <v>1.02482</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.6828</v>
+        <v>0.5457</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.51241</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.57203</v>
+        <v>0.45527</v>
       </c>
       <c r="AL15" t="n">
         <v>1.97</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.97</v>
+        <v>1.211</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.393</v>
+        <v>0.469</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.08696</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.485</v>
+        <v>0.6055</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.54214</v>
+        <v>0.6750699999999999</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AS15" t="n">
         <v>1.31</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AU15" t="n">
         <v>1.31</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AW15" t="n">
         <v>0.655</v>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>1501-16-12-FG</t>
+          <t>1501-12-16-FG</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 1-11 1/2 NPTF x 3/4-14 NPSM (female swivel)</t>
+          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 3/4-14 NPTF x 1-11 1/2 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF</t>
+          <t>3/4-14 NPTF</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3/4-14 NPSM (female swivel)</t>
+          <t>1-11 1/2 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
@@ -3606,19 +3606,19 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>leg 1: male NPTF thread dia at L2 1.3259 vs hex flats 1.3100 (round end proud of the flats by 0.0079; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>leg 2: Air-Way nut face to stem tip (W - M) 0.380 vs Brennan 0.350: nut placed at Air-Way W (user decision 2026-09-24, as 1404/1405)</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>1501-16-12-FG</t>
+          <t>1501-12-16-FG</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1501-16-16-FG</t>
+          <t>1501-16-12-FG</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -3640,67 +3640,67 @@
         <v>0.2572</v>
       </c>
       <c r="H16" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="I16" t="n">
         <v>0.655</v>
       </c>
       <c r="J16" t="n">
-        <v>0.97</v>
+        <v>0.79</v>
       </c>
       <c r="K16" t="n">
-        <v>0.525</v>
+        <v>0.389</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9</v>
+        <v>0.745</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7098</v>
+        <v>0.5694</v>
       </c>
       <c r="N16" t="n">
-        <v>0.175</v>
+        <v>0.135</v>
       </c>
       <c r="O16" t="n">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.86603</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6465</v>
+        <v>0.517</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6055</v>
+        <v>0.485</v>
       </c>
       <c r="T16" t="n">
-        <v>0.428</v>
+        <v>0.361</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6465</v>
+        <v>0.517</v>
       </c>
       <c r="V16" t="n">
-        <v>0.67</v>
+        <v>0.5625</v>
       </c>
       <c r="W16" t="n">
-        <v>0.7447</v>
+        <v>0.6189</v>
       </c>
       <c r="X16" t="n">
-        <v>0.59</v>
+        <v>0.4635</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.4845</v>
+        <v>0.375</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.38</v>
+        <v>0.34</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AC16" t="n">
         <v>0.9399999999999999</v>
@@ -3709,10 +3709,10 @@
         <v>1.97</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.84</v>
+        <v>0.63</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AG16" t="n">
         <v>1.2832</v>
@@ -3733,22 +3733,22 @@
         <v>1.97</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.211</v>
+        <v>0.97</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.469</v>
+        <v>0.393</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.6055</v>
+        <v>0.485</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.6750699999999999</v>
+        <v>0.54214</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AS16" t="n">
         <v>1.31</v>
@@ -3760,7 +3760,7 @@
         <v>1.31</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AW16" t="n">
         <v>0.655</v>
@@ -3779,12 +3779,12 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>1501-16-16-FG</t>
+          <t>1501-16-12-FG</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 1-11 1/2 NPTF x 1-11 1/2 NPSM (female swivel)</t>
+          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 1-11 1/2 NPTF x 3/4-14 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPSM (female swivel)</t>
+          <t>3/4-14 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
@@ -3814,26 +3814,26 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>leg 1: male NPTF thread dia at L2 1.3259 vs hex flats 1.3100 (round end proud of the flats by 0.0079; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012); leg 2: Air-Way nut face to stem tip (W - M) 0.380 vs Brennan 0.350: nut placed at Air-Way W (user decision 2026-09-24, as 1404/1405)</t>
+          <t>leg 1: male NPTF thread dia at L2 1.3259 vs hex flats 1.3100 (round end proud of the flats by 0.0079; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>1501-16-16-FG</t>
+          <t>1501-16-12-FG</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1501-16-20-FG</t>
+          <t>1501-16-16-FG</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8125</v>
+        <v>0.655</v>
       </c>
       <c r="D17" t="n">
         <v>0.6415999999999999</v>
@@ -3848,79 +3848,79 @@
         <v>0.2572</v>
       </c>
       <c r="H17" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8125</v>
+        <v>0.655</v>
       </c>
       <c r="J17" t="n">
-        <v>1.04</v>
+        <v>0.97</v>
       </c>
       <c r="K17" t="n">
-        <v>0.695</v>
+        <v>0.525</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9048</v>
+        <v>0.7098</v>
       </c>
       <c r="N17" t="n">
-        <v>0.195</v>
+        <v>0.175</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9375</v>
+        <v>0.75</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.08253</v>
+        <v>0.86603</v>
       </c>
       <c r="R17" t="n">
-        <v>0.819</v>
+        <v>0.6465</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7775</v>
+        <v>0.6055</v>
       </c>
       <c r="T17" t="n">
-        <v>0.497</v>
+        <v>0.428</v>
       </c>
       <c r="U17" t="n">
-        <v>0.819</v>
+        <v>0.6465</v>
       </c>
       <c r="V17" t="n">
-        <v>0.85</v>
+        <v>0.67</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8141</v>
+        <v>0.7447</v>
       </c>
       <c r="X17" t="n">
-        <v>0.768</v>
+        <v>0.59</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.6405</v>
+        <v>0.4845</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.875</v>
+        <v>1.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.01</v>
+        <v>0.84</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AG17" t="n">
         <v>1.2832</v>
@@ -3938,61 +3938,61 @@
         <v>0.57203</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.555</v>
+        <v>1.211</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.5385</v>
+        <v>0.469</v>
       </c>
       <c r="AO17" t="n">
         <v>0.08696</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.7775</v>
+        <v>0.6055</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.84707</v>
+        <v>0.6750699999999999</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.625</v>
+        <v>1.31</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.41</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.625</v>
+        <v>1.31</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.11</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.8125</v>
+        <v>0.655</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.8125</v>
+        <v>0.655</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.4686</v>
+        <v>0.37766</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.4686</v>
+        <v>0.37766</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.93769</v>
+        <v>0.75583</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>1501-16-20-FG</t>
+          <t>1501-16-16-FG</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 1-11 1/2 NPTF x 1 1/4-11 1/2 NPSM (female swivel)</t>
+          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 1-11 1/2 NPTF x 1-11 1/2 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPSM (female swivel)</t>
+          <t>1-11 1/2 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
@@ -4017,154 +4017,154 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1501-16-20 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N1@DRIVE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-16-20-FG col "L LGTH" = "2.350" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.3, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the male NPTF tip (column mapping: REPORT.md, table 1501); M1@DRIVE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-16-20-FG col "M LGTH" = "1.730" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.3, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the NPSM swivel stem tip (column mapping: REPORT.md, table 1501); W3@HEX: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-16-20-FG col "M1 LGTH" = "2.150" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.3, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the swivel-nut face (column mapping: REPORT.md, table 1501); CHEX@HEX: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-16-20-FG col "C HEX" = "1.875" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.3, page verified True) [Brennan = yes 2026-10-18] - swivel nut hex (column mapping: REPORT.md, table 1501); C1HEX@HEX: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-16-20-FG col "Y FLATS" = "1.625" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.3, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 1501); D2@BORE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-16-20-FG col "A1 DRILL" = "0.938" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.3, page verified True) [Brennan = yes 2026-10-18] - male NPTF end drill (column mapping: REPORT.md, table 1501); D@BORE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-16-20-FG col "A2 DRILL" = "1.010" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.3, page verified True) [Brennan = yes 2026-10-18] - NPSM swivel stem bore (column mapping: REPORT.md, table 1501); THDMAJ_A@DRIVE: end library: pipe OD of the -16 NPTF thread = 1.315 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[16], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A1@DRIVE: end library: pipe OD of the -20 NPSM swivel thread = 1.66 (ASME B1.20.1 pipe OD, ms51500.py NPTF[20]; the value every built 1501 / 1405 / 1502 row carries for its NPSM end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes in the format of the table's other rows; = Brennan TFA-p020-t01 thread columns (A1 NPTF 1-11-1/2, A2 NPSM 1-1/4-11-1/2) and OMi Items Side 1 / 2 / 3 Thread | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging); NUT FACE AT AIR-WAY W3 AND STEM TIP AT AIR-WAY M1/M (crossing to the stem tip) (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way s113 only (double-pass 48 rows) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging); NUT FACE AT AIR-WAY W3 AND STEM TIP AT AIR-WAY M1/M (crossing to the stem tip) (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1501-16-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
+          <t>leg 1: male NPTF thread dia at L2 1.3259 vs hex flats 1.3100 (round end proud of the flats by 0.0079; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012); leg 2: Air-Way nut face to stem tip (W - M) 0.380 vs Brennan 0.350: nut placed at Air-Way W (user decision 2026-09-24, as 1404/1405)</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>1501-16-20-FG</t>
+          <t>1501-16-16-FG</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1501-20-16-FG</t>
+          <t>1501-16-20-FG</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="C18" t="n">
         <v>0.8125</v>
       </c>
       <c r="D18" t="n">
-        <v>0.81335</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7068</v>
+        <v>0.6828</v>
       </c>
       <c r="F18" t="n">
         <v>1.7899</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2632</v>
+        <v>0.2572</v>
       </c>
       <c r="H18" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="I18" t="n">
         <v>0.8125</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="K18" t="n">
-        <v>0.525</v>
+        <v>0.695</v>
       </c>
       <c r="L18" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7098</v>
+        <v>0.9048</v>
       </c>
       <c r="N18" t="n">
-        <v>0.175</v>
+        <v>0.195</v>
       </c>
       <c r="O18" t="n">
-        <v>0.75</v>
+        <v>0.9375</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.86603</v>
+        <v>1.08253</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6465</v>
+        <v>0.819</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6055</v>
+        <v>0.7775</v>
       </c>
       <c r="T18" t="n">
-        <v>0.428</v>
+        <v>0.497</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6465</v>
+        <v>0.819</v>
       </c>
       <c r="V18" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="W18" t="n">
-        <v>0.7447</v>
+        <v>0.8141</v>
       </c>
       <c r="X18" t="n">
-        <v>0.59</v>
+        <v>0.768</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.4845</v>
+        <v>0.6405</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.35</v>
+        <v>0.42</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.5</v>
+        <v>1.875</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.25</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.83</v>
+        <v>1.01</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.6267</v>
+        <v>1.2832</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.7068</v>
+        <v>0.6828</v>
       </c>
       <c r="AI18" t="n">
         <v>0.08696</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.81335</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.74378</v>
+        <v>0.57203</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.211</v>
+        <v>1.555</v>
       </c>
       <c r="AN18" t="n">
-        <v>0.469</v>
+        <v>0.5385</v>
       </c>
       <c r="AO18" t="n">
         <v>0.08696</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.6055</v>
+        <v>0.7775</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.6750699999999999</v>
+        <v>0.84707</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AS18" t="n">
         <v>1.625</v>
@@ -4195,12 +4195,12 @@
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>1501-20-16-FG</t>
+          <t>1501-16-20-FG</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 1 1/4-11 1/2 NPTF x 1-11 1/2 NPSM (female swivel)</t>
+          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 1-11 1/2 NPTF x 1 1/4-11 1/2 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF</t>
+          <t>1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPSM (female swivel)</t>
+          <t>1 1/4-11 1/2 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
@@ -4225,31 +4225,31 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1501-20-16 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N1@DRIVE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-20-16-FG col "L LGTH" = "2.380" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 435.5, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the male NPTF tip (column mapping: REPORT.md, table 1501); M1@DRIVE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-20-16-FG col "M LGTH" = "1.700" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 435.5, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the NPSM swivel stem tip (column mapping: REPORT.md, table 1501); W3@HEX: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-20-16-FG col "M1 LGTH" = "2.050" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 435.5, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the swivel-nut face (column mapping: REPORT.md, table 1501); CHEX@HEX: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-20-16-FG col "C HEX" = "1.500" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 435.5, page verified True) [Brennan = yes 2026-10-18] - swivel nut hex (column mapping: REPORT.md, table 1501); C1HEX@HEX: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-20-16-FG col "Y FLATS" = "1.625" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 435.5, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 1501); D2@BORE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-20-16-FG col "A1 DRILL" = "1.250" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 435.5, page verified True) [Brennan = yes 2026-10-18] - male NPTF end drill (column mapping: REPORT.md, table 1501); D@BORE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-20-16-FG col "A2 DRILL" = "0.830" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 435.5, page verified True) [Brennan = yes 2026-10-18] - NPSM swivel stem bore (column mapping: REPORT.md, table 1501); THDMAJ_A@DRIVE: end library: pipe OD of the -20 NPTF thread = 1.66 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[20], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A1@DRIVE: end library: pipe OD of the -16 NPSM swivel thread = 1.315 (ASME B1.20.1 pipe OD, ms51500.py NPTF[16]; the value every built 1501 / 1405 / 1502 row carries for its NPSM end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes in the format of the table's other rows; = Brennan TFA-p020-t01 thread columns (A1 NPTF 1-1/4-11-1/2, A2 NPSM 1-11-1/2) and OMi Items Side 1 / 2 / 3 Thread | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging); NUT FACE AT AIR-WAY W3 AND STEM TIP AT AIR-WAY M1/M (crossing to the stem tip) (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1501-16-20 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N1@DRIVE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-16-20-FG col "L LGTH" = "2.350" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.3, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the male NPTF tip (column mapping: REPORT.md, table 1501); M1@DRIVE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-16-20-FG col "M LGTH" = "1.730" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.3, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the NPSM swivel stem tip (column mapping: REPORT.md, table 1501); W3@HEX: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-16-20-FG col "M1 LGTH" = "2.150" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.3, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the swivel-nut face (column mapping: REPORT.md, table 1501); CHEX@HEX: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-16-20-FG col "C HEX" = "1.875" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.3, page verified True) [Brennan = yes 2026-10-18] - swivel nut hex (column mapping: REPORT.md, table 1501); C1HEX@HEX: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-16-20-FG col "Y FLATS" = "1.625" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.3, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 1501); D2@BORE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-16-20-FG col "A1 DRILL" = "0.938" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.3, page verified True) [Brennan = yes 2026-10-18] - male NPTF end drill (column mapping: REPORT.md, table 1501); D@BORE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-16-20-FG col "A2 DRILL" = "1.010" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.3, page verified True) [Brennan = yes 2026-10-18] - NPSM swivel stem bore (column mapping: REPORT.md, table 1501); THDMAJ_A@DRIVE: end library: pipe OD of the -16 NPTF thread = 1.315 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[16], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A1@DRIVE: end library: pipe OD of the -20 NPSM swivel thread = 1.66 (ASME B1.20.1 pipe OD, ms51500.py NPTF[20]; the value every built 1501 / 1405 / 1502 row carries for its NPSM end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes in the format of the table's other rows; = Brennan TFA-p020-t01 thread columns (A1 NPTF 1-11-1/2, A2 NPSM 1-1/4-11-1/2) and OMi Items Side 1 / 2 / 3 Thread | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging); NUT FACE AT AIR-WAY W3 AND STEM TIP AT AIR-WAY M1/M (crossing to the stem tip) (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1501-20-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate) | leg 1: male NPTF thread dia at L2 1.6709 vs hex flats 1.6250 (round end proud of the flats by 0.0229; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1501-16-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>1501-20-16-FG</t>
+          <t>1501-16-20-FG</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1501-20-20-FG</t>
+          <t>1501-20-16-FG</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2.38</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8125</v>
       </c>
       <c r="D19" t="n">
         <v>0.81335</v>
@@ -4264,67 +4264,67 @@
         <v>0.2632</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8125</v>
       </c>
       <c r="J19" t="n">
-        <v>1.05</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.695</v>
+        <v>0.525</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9048</v>
+        <v>0.7098</v>
       </c>
       <c r="N19" t="n">
-        <v>0.195</v>
+        <v>0.175</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9375</v>
+        <v>0.75</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.08542</v>
+        <v>0.86603</v>
       </c>
       <c r="R19" t="n">
-        <v>0.819</v>
+        <v>0.6465</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7775</v>
+        <v>0.6055</v>
       </c>
       <c r="T19" t="n">
-        <v>0.497</v>
+        <v>0.428</v>
       </c>
       <c r="U19" t="n">
-        <v>0.819</v>
+        <v>0.6465</v>
       </c>
       <c r="V19" t="n">
-        <v>0.85</v>
+        <v>0.67</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8141</v>
+        <v>0.7447</v>
       </c>
       <c r="X19" t="n">
-        <v>0.768</v>
+        <v>0.59</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.6405</v>
+        <v>0.4845</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.43</v>
+        <v>0.35</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AC19" t="n">
         <v>1.25</v>
@@ -4333,10 +4333,10 @@
         <v>2.38</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.01</v>
+        <v>0.83</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG19" t="n">
         <v>1.6267</v>
@@ -4357,58 +4357,58 @@
         <v>2.38</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.555</v>
+        <v>1.211</v>
       </c>
       <c r="AN19" t="n">
-        <v>0.5385</v>
+        <v>0.469</v>
       </c>
       <c r="AO19" t="n">
         <v>0.08696</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.7775</v>
+        <v>0.6055</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.84707</v>
+        <v>0.6750699999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.63</v>
+        <v>1.625</v>
       </c>
       <c r="AT19" t="n">
         <v>1.41</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.63</v>
+        <v>1.625</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8125</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8125</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.47004</v>
+        <v>0.4686</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.47004</v>
+        <v>0.4686</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.94058</v>
+        <v>0.93769</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>1501-20-20-FG</t>
+          <t>1501-20-16-FG</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 1 1/4-11 1/2 NPTF x 1 1/4-11 1/2 NPSM (female swivel)</t>
+          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 1 1/4-11 1/2 NPTF x 1-11 1/2 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPSM (female swivel)</t>
+          <t>1-11 1/2 NPSM (female swivel)</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
@@ -4433,223 +4433,639 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>Air-Way s113 only (double-pass 48 rows) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging); NUT FACE AT AIR-WAY W3 AND STEM TIP AT AIR-WAY M1/M (crossing to the stem tip) (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 1501-20-16 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N1@DRIVE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-20-16-FG col "L LGTH" = "2.380" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 435.5, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the male NPTF tip (column mapping: REPORT.md, table 1501); M1@DRIVE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-20-16-FG col "M LGTH" = "1.700" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 435.5, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the NPSM swivel stem tip (column mapping: REPORT.md, table 1501); W3@HEX: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-20-16-FG col "M1 LGTH" = "2.050" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 435.5, page verified True) [Brennan = yes 2026-10-18] - axis crossing to the swivel-nut face (column mapping: REPORT.md, table 1501); CHEX@HEX: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-20-16-FG col "C HEX" = "1.500" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 435.5, page verified True) [Brennan = yes 2026-10-18] - swivel nut hex (column mapping: REPORT.md, table 1501); C1HEX@HEX: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-20-16-FG col "Y FLATS" = "1.625" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 435.5, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 1501); D2@BORE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-20-16-FG col "A1 DRILL" = "1.250" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 435.5, page verified True) [Brennan = yes 2026-10-18] - male NPTF end drill (column mapping: REPORT.md, table 1501); D@BORE: Brennan TFA catalog p.20 table TFA-p020-t01 "1501-FG MP-FPS 90 DEG ELBOW" row 1501-20-16-FG col "A2 DRILL" = "0.830" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 435.5, page verified True) [Brennan = yes 2026-10-18] - NPSM swivel stem bore (column mapping: REPORT.md, table 1501); THDMAJ_A@DRIVE: end library: pipe OD of the -20 NPTF thread = 1.66 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[20], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A1@DRIVE: end library: pipe OD of the -16 NPSM swivel thread = 1.315 (ASME B1.20.1 pipe OD, ms51500.py NPTF[16]; the value every built 1501 / 1405 / 1502 row carries for its NPSM end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes in the format of the table's other rows; = Brennan TFA-p020-t01 thread columns (A1 NPTF 1-1/4-11-1/2, A2 NPSM 1-11-1/2) and OMi Items Side 1 / 2 / 3 Thread | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging); NUT FACE AT AIR-WAY W3 AND STEM TIP AT AIR-WAY M1/M (crossing to the stem tip) (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>leg 1: male NPTF thread dia at L2 1.6709 vs hex flats 1.6300 (round end proud of the flats by 0.0204; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 1501-20-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate) | leg 1: male NPTF thread dia at L2 1.6709 vs hex flats 1.6250 (round end proud of the flats by 0.0229; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>1501-20-20-FG</t>
+          <t>1501-20-16-FG</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1501-32-32-FG</t>
+          <t>1501-20-20-FG</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.13</v>
+        <v>2.38</v>
       </c>
       <c r="C20" t="n">
-        <v>1.25</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>1.16929</v>
+        <v>0.81335</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7565</v>
+        <v>0.7068</v>
       </c>
       <c r="F20" t="n">
         <v>1.7899</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2735</v>
+        <v>0.2632</v>
       </c>
       <c r="H20" t="n">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="I20" t="n">
-        <v>1.25</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>1.155</v>
+        <v>1.05</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0215</v>
+        <v>0.695</v>
       </c>
       <c r="L20" t="n">
-        <v>1.125</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2766</v>
+        <v>0.9048</v>
       </c>
       <c r="N20" t="n">
         <v>0.195</v>
       </c>
       <c r="O20" t="n">
-        <v>1.31</v>
+        <v>0.9375</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.51843</v>
+        <v>1.08542</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1755</v>
+        <v>0.819</v>
       </c>
       <c r="S20" t="n">
-        <v>1.134</v>
+        <v>0.7775</v>
       </c>
       <c r="T20" t="n">
-        <v>0.502</v>
+        <v>0.497</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1755</v>
+        <v>0.819</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2125</v>
+        <v>0.85</v>
       </c>
       <c r="W20" t="n">
-        <v>0.9385</v>
+        <v>0.8141</v>
       </c>
       <c r="X20" t="n">
-        <v>1.0985</v>
+        <v>0.768</v>
       </c>
       <c r="Y20" t="n">
-        <v>1</v>
+        <v>0.6405</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.63</v>
+        <v>1.88</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.13</v>
+        <v>2.38</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.33859</v>
+        <v>1.6267</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.7565</v>
+        <v>0.7068</v>
       </c>
       <c r="AI20" t="n">
         <v>0.08696</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.16929</v>
+        <v>0.81335</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.09973</v>
+        <v>0.74378</v>
       </c>
       <c r="AL20" t="n">
-        <v>3.13</v>
+        <v>2.38</v>
       </c>
       <c r="AM20" t="n">
-        <v>2.268</v>
+        <v>1.555</v>
       </c>
       <c r="AN20" t="n">
-        <v>0.5435</v>
+        <v>0.5385</v>
       </c>
       <c r="AO20" t="n">
         <v>0.08696</v>
       </c>
       <c r="AP20" t="n">
+        <v>0.7775</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.84707</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0.47004</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0.47004</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0.94058</v>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>1501-20-20-FG</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 1 1/4-11 1/2 NPTF x 1 1/4-11 1/2 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>1501</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>Air-Way s113 only (double-pass 48 rows) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging); NUT FACE AT AIR-WAY W3 AND STEM TIP AT AIR-WAY M1/M (crossing to the stem tip) (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>leg 1: male NPTF thread dia at L2 1.6709 vs hex flats 1.6300 (round end proud of the flats by 0.0204; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>1501-20-20-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1501-24-24-FG</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.8075</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.22687</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.9385</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.9385</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.9675</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.9392</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.86566</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0.86326</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.794</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0.5445</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0.96657</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.015</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0.53932</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0.53932</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.07915</v>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>1501-24-24-FG</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 1 1/2-11 1/2 NPTF x 1 1/2-11 1/2 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>1501</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>[BRENNAN-CELL 2026-10-20: CHEX@HEX] Air-Way s113 only (double-pass 48 rows); CHEX@HEX: Brennan TFA catalog p.20 table TFA-p020-t01 "MP-FPS 90 DEG ELBOW" row 1501-24-24-FG col "C HEX" = 2.125 (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_index.json, page verified True) [user 2026-10-20 Q1: Air-Way value cannot be built -&gt; Brennan ("use brennans")] (Air-Way printed 1.88: the nut hex 1.88 is smaller than the Brennan -24 NPSM swivel nut (2.125) the generator's nut shape is measured from, and smaller than Air-Way's own non-FG 1501-24-24 nut (2.13); generator BLOCKED ("Air-Way nut hex C(2) 1.88 differs from the Brennan nut 2.125")) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging); NUT FACE AT AIR-WAY W3 AND STEM TIP AT AIR-WAY M1/M (crossing to the stem tip) (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>2026-10-20 CHEX@HEX = Brennan 2.125 (Air-Way 1.88 cannot be built: the nut hex 1.88 is smaller than the Brennan -24 NPSM swivel nut (2.125) the generator's nut shape is measured from, and smaller than Air-Way's own non-FG 1501-24-24 nut (2.13); generator BLOCKED ("Air-Way nut hex C(2) 1.88 differs from the Brennan nut 2.125")) | leg 1: male NPTF thread dia at L2 1.9109 vs hex flats 1.8700 (round end proud of the flats by 0.0204; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012); leg 2: the corner puck (radius 1.080) reaches 0.065 past the swivel body face (1.015) but stays inside the neck (max 0.368 off the axis vs neck radius 0.807) - as on the Brennan 6502-08-08-FG / 1503-08-08-FG forgings; leg 2 hex arm 1.015 barely clears the corner puck (radius 1.080)</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>1501-24-24-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1501-32-32-FG</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.155</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.0215</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.2766</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.51843</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.1755</v>
+      </c>
+      <c r="S22" t="n">
         <v>1.134</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="T22" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.1755</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.2125</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.9385</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.0985</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.33859</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.09973</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>2.268</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0.5435</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="AQ22" t="n">
         <v>1.20357</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="AR22" t="n">
         <v>2.62</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="AS22" t="n">
         <v>2.5</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="AT22" t="n">
         <v>2.1</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="AU22" t="n">
         <v>2.5</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="AV22" t="n">
         <v>1.465</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="AW22" t="n">
         <v>1.25</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="AX22" t="n">
         <v>1.25</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="AY22" t="n">
         <v>0.72119</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="AZ22" t="n">
         <v>0.72119</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BA22" t="n">
         <v>1.44288</v>
       </c>
-      <c r="BB20" t="inlineStr">
+      <c r="BB22" t="inlineStr">
         <is>
           <t>1501-32-32-FG</t>
         </is>
       </c>
-      <c r="BC20" t="inlineStr">
+      <c r="BC22" t="inlineStr">
         <is>
           <t>90 deg Male Pipe x Female NPSM Swivel Elbow, 2-11 1/2 NPTF x 2-11 1/2 NPSM (female swivel)</t>
         </is>
       </c>
-      <c r="BD20" t="inlineStr">
+      <c r="BD22" t="inlineStr">
         <is>
           <t>1501</t>
         </is>
       </c>
-      <c r="BE20" t="inlineStr">
+      <c r="BE22" t="inlineStr">
         <is>
           <t>2-11 1/2 NPTF</t>
         </is>
       </c>
-      <c r="BF20" t="inlineStr">
+      <c r="BF22" t="inlineStr">
         <is>
           <t>2-11 1/2 NPSM (female swivel)</t>
         </is>
       </c>
-      <c r="BG20" t="inlineStr">
+      <c r="BG22" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="BH20" t="inlineStr">
+      <c r="BH22" t="inlineStr">
         <is>
           <t>Air-Way s113 only (double-pass 48 rows) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging); NUT FACE AT AIR-WAY W3 AND STEM TIP AT AIR-WAY M1/M (crossing to the stem tip) (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="BI20" t="inlineStr">
+      <c r="BI22" t="inlineStr">
         <is>
           <t>leg 2 hex arm 1.465 barely clears the corner puck (radius 1.443)</t>
         </is>
       </c>
-      <c r="BJ20" t="inlineStr">
+      <c r="BJ22" t="inlineStr">
         <is>
           <t>1501-32-32-FG</t>
         </is>
